--- a/extenbooks/S1505_extenbook.xlsx
+++ b/extenbooks/S1505_extenbook.xlsx
@@ -9348,7 +9348,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -10547,11 +10547,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10574,64 +10574,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Chapter 15 series S1505</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1505_research.json", "adequacy_report": "Technical/docs/chapters/CH15_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1505_DPR.md", "epr": "Technical/docs/series/S1505_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1505_load.py", "processor": "Technical/code/P02_processors/P02_S1505_construct.py", "validator": "Technical/code/V03_validators/V03_S1505_validate.py", "processed": "Technical/data/processed/S1505.parquet", "chopped_csv": "Technical/chopped/S1505.csv", "extenbook_xlsx": "Technical/extenbooks/S1505_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1505_extenbook.xlsx
+++ b/extenbooks/S1505_extenbook.xlsx
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -5783,7 +5783,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7278,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -8428,7 +8428,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A141"/>
+  <dimension ref="A1:A143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -9334,7 +9334,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Pipeline stage**: Ingestion</t>
         </is>
       </c>
     </row>
@@ -9362,7 +9362,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-fanout-ch15</t>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
         </is>
       </c>
     </row>
@@ -9426,7 +9426,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>- `pi` = `ln(pGDP_t / pGDP_{t-1})` (GDP deflator inflation rate) from BEA NIPA T1.1.4</t>
+          <t>- `pi` = `ln(pGDP_t / pGDP_{t-1})` (GDP deflator inflation rate) from BEA National Income and Product Accounts (NIPA) T1.1.4</t>
         </is>
       </c>
     </row>
@@ -9490,59 +9490,59 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Source | Native units |</t>
+          <t>*Each series is built from sub-components identified by a suffix on the series ID (for example, S1505-A, S1505-B); they are listed below.*</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>| **S1505-pi** | 1948-2010 | BEA NIPA T1.1.4 (GDP deflator); inflation as log-diff | Rate (decimal) |</t>
+          <t>| Subseries | Coverage | Source | Native units |</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>| **S1505-sigma** | 1948-2010 | BEA NIPA T5.3.5 line 2 (Igcorpbea) / T1.16 (NOS) | Rate (decimal) |</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>| **S1505-sigma-prime** | 1948-2010 | normalized sigma per Handfas 2012 (HP-filter detrend) | Rate (decimal) |</t>
+          <t>| **S1505-pi** | 1948-2010 | BEA NIPA T1.1.4 (GDP deflator); inflation as log-diff | Rate (decimal) |</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>| **S1505-uL** | 1948-2010 | BLS Civilian Unemployment Rate via Appendix 14.2 working spreadsheet | Rate (decimal) |</t>
+          <t>| **S1505-sigma** | 1948-2010 | BEA NIPA T5.3.5 line 2 (Igcorpbea) / T1.16 (NOS) | Rate (decimal) |</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>| **S1505-uLintensity** | 1948-2010 | BLS UNEMPLRATE * (duration index) per Appendix 14.2 | Rate (decimal) |</t>
+          <t>| **S1505-sigma-prime** | 1948-2010 | normalized sigma per Handfas 2012 (Hodrick-Prescott (HP) filter detrend) | Rate (decimal) |</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>| **S1505-uL** | 1948-2010 | BLS Civilian Unemployment Rate via Appendix 14.2 working spreadsheet | Rate (decimal) |</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>All five subseries are read from `Appendix15_USInflation.xlsx` (columns `pi`, `sigma`, `sigma'`, `uL`, `uLintensity`) and cross-referenced against `Appendix14_InflationULdata.xlsx` for the BLS unemployment data.</t>
+          <t>| **S1505-uLintensity** | 1948-2010 | BLS UNEMPLRATE * (duration index) per Appendix 14.2 | Rate (decimal) |</t>
         </is>
       </c>
     </row>
@@ -9552,7 +9552,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>All five subseries are read from `Appendix15_USInflation.xlsx` (columns `pi`, `sigma`, `sigma'`, `uL`, `uLintensity`) and cross-referenced against `Appendix14_InflationULdata.xlsx` for the BLS unemployment data.</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9562,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>`composite + formula`. The book values are the authoritative replication target (Shaikh's hand-compiled Appendix 15.1 spreadsheet). The replication loader reads them directly; extension would re-fetch BEA NIPA T1.1.4 (pGDP), T1.16 (NOS), T5.3.5 (investment), and BLS UNRATE via FRED, then recompute.</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
@@ -9572,7 +9572,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>`composite + formula`. The book values are the authoritative replication target (Shaikh's hand-compiled Appendix 15.1 spreadsheet). The replication loader reads them directly; extension would re-fetch BEA NIPA T1.1.4 (pGDP), T1.16 (NOS), T5.3.5 (investment), and BLS UNRATE via FRED, then recompute.</t>
         </is>
       </c>
     </row>
@@ -9582,24 +9582,24 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>## 5. Year coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>- **Book period**: 1948-2010 (annual) — 63 obs.</t>
         </is>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>- **Extension**: feasible; BEA NIPA + BLS UNRATE continuously published. Currently degraded (BEA API client not yet implemented; UNRATE extension via FRED would require a Phase 7 enhancement). Book-period values published as-is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>## 6. Units</t>
+          <t>- **Extension**: feasible; BEA NIPA + BLS UNRATE continuously published. Currently degraded (BEA API client not yet implemented; UNRATE extension via FRED would require a future enhancement). Book-period values published as-is.</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>All subseries are dimensionless rates (decimal). BLS UNRATE published as percent in source; the loader normalizes to decimal (divide by 100).</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
@@ -9619,7 +9619,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>All subseries are dimensionless rates (decimal). BLS UNRATE published as percent in source; the loader normalizes to decimal (divide by 100).</t>
         </is>
       </c>
     </row>
@@ -9629,38 +9629,38 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1. **BEA T1.16 row-label validation**: per Phase 4 Q4 resolution, T1.16 line ordering varies by vintage; the loader (when BEA API integrated) must validate by ROW LABEL "Net operating surplus", not numeric line position. The chopped values use Shaikh's 2012 vintage and are authoritative for replication.</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2. **NOS vs gross-investment alternative**: Shaikh footnote 1 in Appendix 15.1 mentions an alternative sigma denominator (gross investment). We retain Handfas 2012 NOS for fidelity.</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3. **uL unit normalization**: book values are decimal; BLS UNRATE on FRED is percent; loader must apply /100.</t>
+          <t>1. **BEA T1.16 row-label validation**: per the data-adequacy review, T1.16 line ordering varies by vintage; the loader (when BEA API integrated) must validate by ROW LABEL "Net operating surplus", not numeric line position. The chopped values use Shaikh's 2012 vintage and are authoritative for replication.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4. **No proxy**: BLS UNRATE, BEA NIPA — same sources Shaikh used.</t>
+          <t>2. **NOS vs gross-investment alternative**: Shaikh footnote 1 in Appendix 15.1 mentions an alternative sigma denominator (gross investment). We retain Handfas 2012 NOS for fidelity.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>3. **uL unit normalization**: book values are decimal; BLS UNRATE on FRED is percent; loader must apply /100.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>4. **No proxy**: BLS UNRATE, BEA NIPA — same sources Shaikh used.</t>
         </is>
       </c>
     </row>
@@ -9670,24 +9670,24 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>- **CD legacy IDs**: `S085` (pi-uL Phillips), `S088`, `S089`</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 15, Figures 15.6-15.8; Appendix 15.1 p. 896</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>- **Predecessor-build IDs**: `S085` (pi-uL Phillips), `S088`, `S089`</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>- **Book reference**: Shaikh (2016), Ch. 15, Figures 15.6-15.8; Appendix 15.1 p. 896</t>
         </is>
       </c>
     </row>
@@ -9697,82 +9697,82 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>- **Tolerance**: +/- 1.0% per (year, subseries) on 1948-2010 against book columns.</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>- **Expected MAE**: near zero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="4">
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>- **Expected mean absolute error (MAE)**: near zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4">
         <f>== EPR: S1505_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t># S1505 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr"/>
-    </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>**Series**: S1505 — Phillips-type curves (parent series)</t>
+          <t># S1505 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
+      <c r="A80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>**Construction classification**: `composite + formula`</t>
+          <t>**Series**: S1505 — Phillips-type curves (parent series)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>**Extension method**: re-fetch BEA NIPA T1.1.4 (pGDP), T1.16 (NOS), T5.3.5 line 2 (Igcorpbea) via BEA API; BLS UNRATE via FRED; recompute pi, sigma, sigma', uL</t>
+          <t>**Pipeline stage**: Extension</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t>**Construction classification**: `composite + formula`</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-fanout-ch15</t>
+          <t>**Extension method**: re-fetch BEA National Income and Product Accounts (NIPA) T1.1.4 (pGDP), T1.16 (NOS), T5.3.5 line 2 (Igcorpbea) via BEA API; BLS UNRATE via FRED; recompute pi, sigma, sigma', uL</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
         </is>
       </c>
     </row>
@@ -9782,7 +9782,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>## 1. Why this series is extendable</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S1505 is `time_series + composite`; all components remain published. Extension recomputes the formulas — not a lazy splice.</t>
+          <t>## 1. Why this series is extendable</t>
         </is>
       </c>
     </row>
@@ -9802,7 +9802,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>## 2. Method</t>
+          <t>S1505 is `time_series + composite`; all components remain published. Extension recomputes the formulas — not a lazy splice.</t>
         </is>
       </c>
     </row>
@@ -9812,121 +9812,121 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>## 2. Method</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>INPUTS (book period, authoritative)</t>
-        </is>
-      </c>
+      <c r="A95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">  S1505_book = Appendix15_USInflation.xlsx cols pi, sigma, sigma', uL, uLintensity</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">               + Appendix14_InflationULdata.xlsx for BLS series cross-ref</t>
+          <t>INPUTS (book period, authoritative)</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  S1505_book = Appendix15_USInflation.xlsx cols pi, sigma, sigma', uL, uLintensity</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>INPUTS (extension period, re-fetched)</t>
+          <t xml:space="preserve">               + Appendix14_InflationULdata.xlsx for BLS series cross-ref</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  BEA NIPA T1.1.4 GDP deflator</t>
-        </is>
-      </c>
+      <c r="A100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">  BEA NIPA T1.16 row "Net operating surplus" (validate by label not line number)</t>
+          <t>INPUTS (extension period, re-fetched)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">  BEA NIPA T5.3.5 line 2 Nonresidential Private Fixed Investment (Igcorpbea)</t>
+          <t xml:space="preserve">  BEA NIPA T1.1.4 GDP deflator</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FRED UNRATE (BLS Civilian Unemployment Rate, percent) - normalize /100</t>
+          <t xml:space="preserve">  BEA NIPA T1.16 row "Net operating surplus" (validate by label not line number)</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BEA NIPA T5.3.5 line 2 Nonresidential Private Fixed Investment (Igcorpbea)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FORMULAS</t>
+          <t xml:space="preserve">  FRED UNRATE (BLS Civilian Unemployment Rate, percent) - normalize /100</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  pi_t      = ln(pGDP_t / pGDP_{t-1})</t>
-        </is>
-      </c>
+      <c r="A106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">  sigma_t   = Igcorpbea_t / NOS_t</t>
+          <t>FORMULAS</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">  sigma'_t  = HP-filter normalize sigma per Handfas 2012</t>
+          <t xml:space="preserve">  pi_t      = ln(pGDP_t / pGDP_{t-1})</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">  uL_t      = UNRATE_t / 100</t>
+          <t xml:space="preserve">  sigma_t   = Igcorpbea_t / NOS_t</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  sigma'_t  = Hodrick-Prescott (HP) filter normalize sigma per Handfas 2012</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  uL_t      = UNRATE_t / 100</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>## 3. No-proxy disclosure</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -9936,7 +9936,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>**None.** BEA NIPA + BLS UNRATE are the same sources Shaikh used. FRED republishes BLS UNRATE without modification.</t>
+          <t>## 3. No-proxy disclosure</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>## 4. No-synthetic disclosure</t>
+          <t>**None.** BEA NIPA + BLS UNRATE are the same sources Shaikh used. FRED republishes BLS UNRATE without modification.</t>
         </is>
       </c>
     </row>
@@ -9956,7 +9956,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>**None.** Missing extension years are simply not appended.</t>
+          <t>## 4. No-synthetic disclosure</t>
         </is>
       </c>
     </row>
@@ -9966,7 +9966,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>## 5. Failure-mode table</t>
+          <t>**None.** Missing extension years are simply not appended.</t>
         </is>
       </c>
     </row>
@@ -9976,52 +9976,52 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>| Failure | Detection | Action |</t>
+          <t>## 5. Failure-mode table</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>| `BEA_API_KEY` missing | `S00_config` | Book period only published |</t>
+          <t>| Failure | Detection | Action |</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>| `FRED_API_KEY` missing | `S00_config` | uL extension skipped |</t>
+          <t>|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>| BEA T1.16 row label changed | label-validation in loader | Warn + skip; document |</t>
+          <t>| `BEA_API_KEY` missing | `S00_config` | Book period only published |</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>| Handfas 2012 sigma formula needs vintage adjustment | manual review | Documented in Phase 9 audit |</t>
+          <t>| `FRED_API_KEY` missing | `S00_config` | uL extension skipped |</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr"/>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>| BEA T1.16 row label changed | label-validation in loader | Warn + skip; document |</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>## 6. CD2 divergence pre-disclosure</t>
+          <t>| Handfas 2012 sigma formula needs vintage adjustment | manual review | Documented in a future audit |</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CD2's S085/S088/S089 used similar BEA/BLS sources; level values expected to match within rounding.</t>
+          <t>## 6. Divergence from the predecessor build</t>
         </is>
       </c>
     </row>
@@ -10041,7 +10041,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>The predecessor build's S085/S088/S089 used similar BEA/BLS sources; level values expected to match within rounding.</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10051,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>## Note on S1506 and S1507 (derived sub-periods)</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -10061,33 +10061,43 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S1506 (1948-1981) and S1507 (1982-2010) are deterministic sub-period slices of S1505. They do NOT independently fetch sources; their loaders read `S1505.parquet` and filter to the relevant year range. See:</t>
+          <t>## Note on S1506 and S1507 (derived sub-periods)</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>- `Technical/code/L01_loaders/L01_S1506_load.py`</t>
-        </is>
-      </c>
+      <c r="A138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>- `Technical/code/L01_loaders/L01_S1507_load.py`</t>
+          <t>S1506 (1948-1981) and S1507 (1982-2010) are deterministic sub-period slices of S1505. They do NOT independently fetch sources; their loaders read `S1505.parquet` and filter to the relevant year range. See:</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>- `Technical/docs/series/S1506_DPR.md`</t>
+          <t>- `Technical/code/L01_loaders/L01_S1506_load.py`</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
+        <is>
+          <t>- `Technical/code/L01_loaders/L01_S1507_load.py`</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>- `Technical/docs/series/S1506_DPR.md`</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>- `Technical/docs/series/S1507_DPR.md`</t>
         </is>
@@ -10532,7 +10542,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-18T22:14:08.276353+00:00</t>
+          <t>2026-07-10T14:18:45.422374+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1505_extenbook.xlsx
+++ b/extenbooks/S1505_extenbook.xlsx
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-10T14:18:45.422374+00:00</t>
+          <t>2026-07-11T03:44:23.427146+00:00</t>
         </is>
       </c>
     </row>
@@ -10557,11 +10557,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10584,6 +10584,150 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_2016_APPENDIX_15_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful composite replication of book figure 15.7. Provides the variables for both the classical curve (inflation vs unutilized growth capacity 1-sigma') and the conventional curve (inflation vs unemployment). Source map (BEA NIPA T1.1.4, T5.3.5, T1.16; BLS unemployment; Handfas 2012 sigma construction) verified against Appendix 15.1 p.896. Per-subseries units split because sigma-prime is a normalized z-score, not a rate.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1505_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1505_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>per_subseries</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
